--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\SCM_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECB21DE-BC31-4607-BAE1-5932AC4D59F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CEC3A7-021B-4F9E-8A95-1886830A7708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11475" yWindow="2070" windowWidth="16125" windowHeight="11610" activeTab="1" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
+    <workbookView xWindow="10245" yWindow="2820" windowWidth="16125" windowHeight="11610" activeTab="1" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>상품코드</t>
   </si>
@@ -37,32 +37,31 @@
     <t>입고예정수량</t>
   </si>
   <si>
-    <t>BK001</t>
-  </si>
-  <si>
-    <t>BK002</t>
-  </si>
-  <si>
-    <t>BK003</t>
-  </si>
-  <si>
-    <t>BK004</t>
-  </si>
-  <si>
-    <t>BK005</t>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>판매수량</t>
+  </si>
+  <si>
+    <t>매출액</t>
+  </si>
+  <si>
+    <t>CR002</t>
+  </si>
+  <si>
+    <t>CR003</t>
+  </si>
+  <si>
+    <t>CR001</t>
+  </si>
+  <si>
+    <t>CR004</t>
+  </si>
+  <si>
+    <t>CR005</t>
   </si>
   <si>
     <t>현재재고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>판매수량</t>
-  </si>
-  <si>
-    <t>매출액</t>
   </si>
 </sst>
 </file>
@@ -456,7 +455,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -467,10 +466,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
         <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>45</v>
       </c>
       <c r="C2" s="3">
         <v>46113</v>
@@ -481,58 +480,58 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3">
-        <v>46108</v>
+        <v>46122</v>
       </c>
       <c r="D3" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>46127</v>
+        <v>46107</v>
       </c>
       <c r="D4" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3">
-        <v>46107</v>
+        <v>46127</v>
       </c>
       <c r="D5" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
         <v>7</v>
       </c>
-      <c r="B6" s="2">
-        <v>67</v>
-      </c>
       <c r="C6" s="3">
-        <v>46122</v>
+        <v>46109</v>
       </c>
       <c r="D6" s="2">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -543,94 +542,109 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA14E83-1FA5-4ABB-BA20-97EE25AE90A4}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>46105</v>
+        <v>46092</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
         <v>3</v>
       </c>
-      <c r="C2" s="2">
-        <v>5</v>
-      </c>
       <c r="D2" s="2">
-        <v>75000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>46105</v>
+        <v>46093</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2">
-        <v>96000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>46105</v>
+        <v>46099</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
         <v>5</v>
       </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
       <c r="D4" s="2">
-        <v>38000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>46106</v>
+        <v>46100</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2">
-        <v>120000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>46106</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2">
-        <v>120000</v>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2">
+        <v>160000</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\SCM_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CEC3A7-021B-4F9E-8A95-1886830A7708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3540B26-0514-451B-B43A-69CBCA347C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="2820" windowWidth="16125" windowHeight="11610" activeTab="1" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>상품코드</t>
   </si>
@@ -46,22 +46,26 @@
     <t>매출액</t>
   </si>
   <si>
-    <t>CR002</t>
-  </si>
-  <si>
-    <t>CR003</t>
-  </si>
-  <si>
-    <t>CR001</t>
-  </si>
-  <si>
-    <t>CR004</t>
-  </si>
-  <si>
-    <t>CR005</t>
-  </si>
-  <si>
     <t>현재재고</t>
+  </si>
+  <si>
+    <t>BK001</t>
+  </si>
+  <si>
+    <t>BK002</t>
+  </si>
+  <si>
+    <t>BK003</t>
+  </si>
+  <si>
+    <t>BK004</t>
+  </si>
+  <si>
+    <t>BK005</t>
+  </si>
+  <si>
+    <t>BK_TEST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -116,7 +120,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -128,6 +132,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81CC86D-72CC-4366-B931-38A2BAA68637}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.125" customWidth="1"/>
@@ -455,7 +462,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -466,7 +473,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <v>3</v>
@@ -480,7 +487,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
         <v>120</v>
@@ -494,7 +501,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -508,7 +515,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>60</v>
@@ -522,7 +529,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
         <v>7</v>
@@ -532,6 +539,20 @@
       </c>
       <c r="D6" s="2">
         <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>46325</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -542,7 +563,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA14E83-1FA5-4ABB-BA20-97EE25AE90A4}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -568,7 +589,7 @@
         <v>46092</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -582,7 +603,7 @@
         <v>46093</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2">
         <v>5</v>
@@ -596,7 +617,7 @@
         <v>46099</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2">
         <v>5</v>
@@ -610,7 +631,7 @@
         <v>46100</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2">
         <v>5</v>
@@ -624,7 +645,7 @@
         <v>46105</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -638,13 +659,27 @@
         <v>46106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2">
         <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>160000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\SCM_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3540B26-0514-451B-B43A-69CBCA347C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99815B1B-7E7B-468C-BE3F-1EB3B26F9CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>BK005</t>
   </si>
   <si>
-    <t>BK_TEST</t>
+    <t>A_TEST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,7 +546,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>5</v>
+        <v>700</v>
       </c>
       <c r="C7" s="4">
         <v>46325</v>
@@ -670,13 +670,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>46106</v>
+        <v>46078</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2">
         <v>50000</v>

--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\SCM_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99815B1B-7E7B-468C-BE3F-1EB3B26F9CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F186FDAA-F468-449F-BF99-5B4979C87F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
+    <workbookView xWindow="6270" yWindow="2235" windowWidth="16125" windowHeight="11610" xr2:uid="{C37867A1-EE11-4720-8686-3A3193102407}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="1" r:id="rId1"/>
@@ -546,7 +546,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="C7" s="4">
         <v>46325</v>
